--- a/Results/pam_parametrizer_diagnostics_ecolicore_all.xlsx
+++ b/Results/pam_parametrizer_diagnostics_ecolicore_all.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="19">
   <si>
     <t>run_id</t>
   </si>
@@ -36,88 +36,34 @@
     <t>ga_error</t>
   </si>
   <si>
-    <t>3.1.3.5</t>
+    <t>E1</t>
   </si>
   <si>
-    <t>3.1.3.97</t>
+    <t>E2</t>
   </si>
   <si>
-    <t>4.1.3.42</t>
+    <t>E3</t>
   </si>
   <si>
-    <t>E116</t>
-  </si>
-  <si>
-    <t>2.6.1.55</t>
-  </si>
-  <si>
-    <t>2.8.3.9</t>
-  </si>
-  <si>
-    <t>E53</t>
-  </si>
-  <si>
-    <t>4.2.1.17</t>
-  </si>
-  <si>
-    <t>5.3.1.25</t>
-  </si>
-  <si>
-    <t>E278</t>
-  </si>
-  <si>
-    <t>2.3.3.9</t>
-  </si>
-  <si>
-    <t>2.5.1.18</t>
-  </si>
-  <si>
-    <t>2.7.2.2</t>
+    <t>E5</t>
   </si>
   <si>
     <t>f</t>
   </si>
   <si>
-    <t>PGK</t>
+    <t>b</t>
   </si>
   <si>
-    <t>GAPD</t>
+    <t>R1</t>
   </si>
   <si>
-    <t>PTAr</t>
+    <t>R2</t>
   </si>
   <si>
-    <t>CYTBD</t>
+    <t>R3</t>
   </si>
   <si>
-    <t>PYK</t>
-  </si>
-  <si>
-    <t>ENO</t>
-  </si>
-  <si>
-    <t>FBA</t>
-  </si>
-  <si>
-    <t>O2t</t>
-  </si>
-  <si>
-    <t>MDH</t>
-  </si>
-  <si>
-    <t>PPC</t>
-  </si>
-  <si>
-    <t>GLCpts</t>
-  </si>
-  <si>
-    <t>FUM</t>
-  </si>
-  <si>
-    <t>ACONTb</t>
-  </si>
-  <si>
-    <t>MALS</t>
+    <t>R5</t>
   </si>
   <si>
     <t>time_s</t>
@@ -484,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -515,16 +461,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>36.91777823627848</v>
+        <v>277.7777777777778</v>
       </c>
       <c r="F2">
-        <v>-0.8202182542714902</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -532,19 +478,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>145.6688788916344</v>
+        <v>277.7777777777778</v>
       </c>
       <c r="F3">
-        <v>-0.8202182542714902</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -552,19 +498,19 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>37.86000088202205</v>
+        <v>138.8888888888889</v>
       </c>
       <c r="F4">
-        <v>-0.8202182542714902</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -572,259 +518,859 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>199.3618211706029</v>
+        <v>138.8888888888889</v>
       </c>
       <c r="F5">
-        <v>-0.8202182542714902</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>28.01533880403535</v>
+        <v>277.7777777777778</v>
       </c>
       <c r="F6">
-        <v>0.09896401797725778</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E7">
-        <v>46.97467317619871</v>
+        <v>277.7777777777778</v>
       </c>
       <c r="F7">
-        <v>0.09896401797725778</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E8">
-        <v>14.579301570853</v>
+        <v>277.7777777777778</v>
       </c>
       <c r="F8">
-        <v>0.09896401797725778</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
       <c r="E9">
-        <v>11</v>
+        <v>277.7777777777778</v>
       </c>
       <c r="F9">
-        <v>0.09896401797725778</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
         <v>13</v>
       </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
       <c r="E10">
-        <v>1.449248645936993</v>
+        <v>138.8888888888889</v>
       </c>
       <c r="F10">
-        <v>0.5855303473150973</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E11">
-        <v>9.555609445366104</v>
+        <v>138.8888888888889</v>
       </c>
       <c r="F11">
-        <v>0.5855303473150973</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E12">
-        <v>85.20397923447001</v>
+        <v>277.7777777777778</v>
       </c>
       <c r="F12">
-        <v>0.5855303473150973</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E13">
-        <v>97.66342046970531</v>
+        <v>277.7777777777778</v>
       </c>
       <c r="F13">
-        <v>0.5855303473150973</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E14">
-        <v>1.890700000000001</v>
+        <v>277.7777777777778</v>
       </c>
       <c r="F14">
-        <v>0.5995355389586875</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E15">
-        <v>35.5401588411239</v>
+        <v>138.8888888888889</v>
       </c>
       <c r="F15">
-        <v>0.5995355389586875</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E16">
-        <v>3.759500000000001</v>
+        <v>277.7777777777778</v>
       </c>
       <c r="F16">
-        <v>0.5995355389586875</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17">
+        <v>277.7777777777778</v>
+      </c>
+      <c r="F17">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" t="s">
         <v>13</v>
       </c>
-      <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17">
-        <v>0.459473767220015</v>
-      </c>
-      <c r="F17">
-        <v>0.5995355389586875</v>
+      <c r="E18">
+        <v>138.8888888888889</v>
+      </c>
+      <c r="F18">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19">
+        <v>277.7777777777778</v>
+      </c>
+      <c r="F19">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20">
+        <v>277.7777777777778</v>
+      </c>
+      <c r="F20">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21">
+        <v>277.7777777777778</v>
+      </c>
+      <c r="F21">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22">
+        <v>138.8888888888889</v>
+      </c>
+      <c r="F22">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23">
+        <v>138.8888888888889</v>
+      </c>
+      <c r="F23">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24">
+        <v>277.7777777777778</v>
+      </c>
+      <c r="F24">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25">
+        <v>277.7777777777778</v>
+      </c>
+      <c r="F25">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26">
+        <v>277.7777777777778</v>
+      </c>
+      <c r="F26">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27">
+        <v>138.8888888888889</v>
+      </c>
+      <c r="F27">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28">
+        <v>125</v>
+      </c>
+      <c r="F28">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29">
+        <v>125</v>
+      </c>
+      <c r="F29">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30">
+        <v>277.7777777777778</v>
+      </c>
+      <c r="F30">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31">
+        <v>138.8888888888889</v>
+      </c>
+      <c r="F31">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32">
+        <v>125.0000000000001</v>
+      </c>
+      <c r="F32">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33">
+        <v>277.7777777777778</v>
+      </c>
+      <c r="F33">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>3</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34">
+        <v>138.8888888888889</v>
+      </c>
+      <c r="F34">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35">
+        <v>125.0000000000001</v>
+      </c>
+      <c r="F35">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>1</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36">
+        <v>277.7777777777778</v>
+      </c>
+      <c r="F36">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>1</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37">
+        <v>277.7777777777778</v>
+      </c>
+      <c r="F37">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>1</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38">
+        <v>138.8888888888889</v>
+      </c>
+      <c r="F38">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>1</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39">
+        <v>138.8888888888889</v>
+      </c>
+      <c r="F39">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>1</v>
+      </c>
+      <c r="B40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40">
+        <v>125</v>
+      </c>
+      <c r="F40">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>1</v>
+      </c>
+      <c r="B41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41">
+        <v>125</v>
+      </c>
+      <c r="F41">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>2</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42">
+        <v>277.7777777777778</v>
+      </c>
+      <c r="F42">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>2</v>
+      </c>
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43">
+        <v>138.8888888888889</v>
+      </c>
+      <c r="F43">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>2</v>
+      </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44">
+        <v>125.0000000000001</v>
+      </c>
+      <c r="F44">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45">
+        <v>277.7777777777778</v>
+      </c>
+      <c r="F45">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>3</v>
+      </c>
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46">
+        <v>138.8888888888889</v>
+      </c>
+      <c r="F46">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>3</v>
+      </c>
+      <c r="B47" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47">
+        <v>125.0000000000001</v>
+      </c>
+      <c r="F47">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -834,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -842,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -853,43 +1399,120 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>137.6650747770036</v>
+        <v>1.693201415007934</v>
       </c>
       <c r="C2">
-        <v>0.03824029854916767</v>
+        <v>0.0004703337263910928</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>148.6227704460034</v>
+        <v>3.900339757004986</v>
       </c>
       <c r="C3">
-        <v>0.04128410290166762</v>
+        <v>0.001083427710279163</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>156.2142831759993</v>
+        <v>3.481582212989451</v>
       </c>
       <c r="C4">
-        <v>0.04339285643777759</v>
+        <v>0.0009671061702748476</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>116.5595775990078</v>
+        <v>3.885442907980178</v>
       </c>
       <c r="C5">
-        <v>0.03237766044416882</v>
+        <v>0.00107928969666116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>4.040983137994772</v>
+      </c>
+      <c r="C6">
+        <v>0.001122495316109659</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>2.691653705987846</v>
+      </c>
+      <c r="C7">
+        <v>0.000747681584996624</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>2.427205302985385</v>
+      </c>
+      <c r="C8">
+        <v>0.0006742236952737181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>2.327969292993657</v>
+      </c>
+      <c r="C9">
+        <v>0.0006466581369426826</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>2.587173269013874</v>
+      </c>
+      <c r="C10">
+        <v>0.0007186592413927429</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2.106683384015923</v>
+      </c>
+      <c r="C11">
+        <v>0.000585189828893312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>2.048389731993666</v>
+      </c>
+      <c r="C12">
+        <v>0.0005689971477760183</v>
       </c>
     </row>
   </sheetData>
@@ -899,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -907,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -915,7 +1538,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>-0.8202182152625973</v>
+        <v>0.5633157774907203</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -923,7 +1546,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.09896398025534218</v>
+        <v>0.5633157774907203</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -931,7 +1554,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.5855303662288054</v>
+        <v>0.5633157774907203</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -939,7 +1562,271 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.5995355383471604</v>
+        <v>0.5633157774907203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>0.5717295532873161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>0.4945987910940497</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>0.4945987910940497</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>0.4945987910940497</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>0.4945987910940497</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>0.575368291632702</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>0.4788182197122368</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>0.6621492027707214</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>0.4876351625259302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>0.6644581373996019</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>0.6644581373996019</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <v>0.6644581373996019</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>4</v>
+      </c>
+      <c r="B18">
+        <v>0.6644581373996019</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19">
+        <v>0.5990257180682013</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <v>0.502815454462027</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>0.502815454462027</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>0.502815454462027</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>4</v>
+      </c>
+      <c r="B23">
+        <v>0.502815454462027</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24">
+        <v>0.626001359668155</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <v>0.6669663377802859</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>3</v>
+      </c>
+      <c r="B26">
+        <v>0.3155644639142784</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>0.3155644639142783</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>3</v>
+      </c>
+      <c r="B31">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>1</v>
+      </c>
+      <c r="B33">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>2</v>
+      </c>
+      <c r="B34">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>1</v>
+      </c>
+      <c r="B36">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>2</v>
+      </c>
+      <c r="B37">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>3</v>
+      </c>
+      <c r="B38">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
